--- a/investor_forms/019_equity_accelerator_application--investor_forms.xlsx
+++ b/investor_forms/019_equity_accelerator_application--investor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'equity',_'value':_'equity'}</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Equity', 'value': 'equity'}</t>
+          <t>Equity</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'diversity,_equity_&amp;_inclusion',_'value':_'diversity_equality_inclusion'}</t>
+          <t>diversity,_equity_&amp;_inclusion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Diversity, Equity &amp; Inclusion', 'value': 'diversity_equality_inclusion'}</t>
+          <t>Diversity, Equity &amp; Inclusion</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'social_impact',_'value':_'social_impact'}</t>
+          <t>social_impact</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Social Impact', 'value': 'social_impact'}</t>
+          <t>Social Impact</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'equity_accelerator',_'value':_'equity_accelerator'}</t>
+          <t>equity_accelerator</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Equity Accelerator', 'value': 'equity_accelerator'}</t>
+          <t>Equity Accelerator</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'incubator',_'value':_'incubator'}</t>
+          <t>incubator</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Incubator', 'value': 'incubator'}</t>
+          <t>Incubator</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
